--- a/artfynd/A 17692-2022 artfynd.xlsx
+++ b/artfynd/A 17692-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17692-2022 artfynd.xlsx
+++ b/artfynd/A 17692-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108018481</v>
+        <v>108018714</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Andsjömyrarna, Jmt</t>
+          <t>Höa, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410163.6740967254</v>
+        <v>409488</v>
       </c>
       <c r="R2" t="n">
-        <v>7013632.858452917</v>
+        <v>7014440</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,27 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-04-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-04-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, flera träd.</t>
+          <t>2023-04-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,6 +773,217 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>108018742</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80433</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Höa, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>409496</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7014437</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>108018481</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Andsjömyrarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>410164</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7013633</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-04-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-04-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, flera träd.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17692-2022 artfynd.xlsx
+++ b/artfynd/A 17692-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108018714</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108018742</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,8 +999,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108018481</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>